--- a/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/00_BANG_TONG_HOP_CAT_THEP_THEO_PHI.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/00_BANG_TONG_HOP_CAT_THEP_THEO_PHI.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +42,12 @@
     <font>
       <name val="Times New Roman"/>
       <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="001F3A5E"/>
       <sz val="10"/>
     </font>
     <font>
@@ -109,12 +115,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -136,7 +143,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -147,23 +154,23 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -531,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N19"/>
+  <dimension ref="B2:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -546,8 +553,10 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -571,709 +580,859 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Thanh dài hơn 11.7m: tách thành số đoạn tối thiểu, mỗi đoạn ≥ 40d; nối chồng 40d ĐÃ GỒM trong chiều dài BBS nên tổng các đoạn = chiều dài BBS (không cộng thêm).</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Đường kính (Ø)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Mô tả hạng mục kết cấu chính</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Số thanh thiết kế (BBS)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Tổng chiều dài (m)</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Số cây 11.7m cần mua</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Khối lượng thép mua (kg)</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Chiều dài phế/đề-xê (m)</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Tỷ lệ hao hụt (%)</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Số mẫu cắt (Patterns)</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Số mối nối đề xuất</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Thanh CHƯA lập kế hoạch cắt (dài hơn cây, chưa có vùng nối)</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>KL thép CHƯA lập kế hoạch (kg)</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>Trạm gia công phụ trách</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>Trạng thái tối ưu</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Ø06</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Thép Ø6 (theo bản vẽ thẩm định: gờ lan can, khe co giãn...)</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>460</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>263.6</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>0.01231884057971015</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>Trạm máy uốn đai CNC nhỏ</t>
+        </is>
+      </c>
+      <c r="P7" s="13" t="inlineStr">
+        <is>
+          <t>OPTIMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Ø08</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Thép đai tăng cường, cấu tạo bản mặt cầu</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n">
-        <v>780</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>543.76</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>217.2</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>0.004500818330605565</v>
-      </c>
-      <c r="K7" s="11" t="n">
+      <c r="E8" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>60.59</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>0.1315242165242165</v>
+      </c>
+      <c r="K8" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>Trạm máy uốn đai CNC nhỏ</t>
+        </is>
+      </c>
+      <c r="P8" s="13" t="inlineStr">
+        <is>
+          <t>OPTIMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Ø10</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Thép cuộn, đai xoắn cọc khoan nhồi, bản mặt cầu</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>7419</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>19352.59</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>1663</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>12005</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>0.003536601035097728</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" s="12" t="n">
+        <v>1384</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>Trạm máy duỗi uốn tự động CNC</t>
+        </is>
+      </c>
+      <c r="P9" s="13" t="inlineStr">
+        <is>
+          <t>OPTIMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Ø12</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Thép thanh vằn cấu tạo, lưới phân bố</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>77681</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>138949.04</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>11906</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>123698.6</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>0.0001599638765773488</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="L10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>Trạm máy cắt đa thanh Shearline</t>
+        </is>
+      </c>
+      <c r="P10" s="13" t="inlineStr">
+        <is>
+          <t>OPTIMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Ø14</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Thép sườn/cánh dầm Super-T, bản mặt cầu</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>3856</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>28699.85</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>2463</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>34811.1</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>102.73</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>0.003564758424685343</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>1512</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>Trạm máy cắt đa thanh Shearline</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="inlineStr">
+        <is>
+          <t>OPTIMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Ø16</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Thép sườn dầm Super-T, dầm ngang, bản mặt cầu</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>36493</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>149520.08</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>13415</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>247675.8</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>7317.57</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>0.04662197246990389</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>492</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>Trạm máy cắt phân đoạn lớn</t>
+        </is>
+      </c>
+      <c r="P12" s="13" t="inlineStr">
+        <is>
+          <t>FEASIBLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Ø18</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Thép thân mố, thân trụ, bản mặt cầu</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>7530</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>37602.6</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>3227</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>75436.3</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>123.61</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>0.00327384594195874</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L13" s="12" t="n">
+        <v>1636</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>Trạm cắt uốn định hình bệ/thân</t>
+        </is>
+      </c>
+      <c r="P13" s="13" t="inlineStr">
+        <is>
+          <t>OPTIMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Ø20</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Thép phân bố bệ mố, bệ trụ T1, T2</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>3897</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>4703.04</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>11656.3</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>0.001331767792163831</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>Trạm cắt uốn định hình móng</t>
+        </is>
+      </c>
+      <c r="P14" s="13" t="inlineStr">
+        <is>
+          <t>OPTIMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Ø22</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Thép tăng cường chịu lực xà mũ, dầm ngang</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>182</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>1409.41</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>167</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>5830.4</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>544.41</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>0.2786283842571268</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>Trạm cắt uốn thanh nặng</t>
+        </is>
+      </c>
+      <c r="P15" s="13" t="inlineStr">
+        <is>
+          <t>OPTIMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="L7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>Trạm máy uốn đai CNC nhỏ</t>
-        </is>
-      </c>
-      <c r="N7" s="12" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Ø25</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Thép chủ cọc khoan nhồi D1200, liên tục nhiệt</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>2808</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>25549.61</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>2302</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>103774.4</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>1381.14</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>0.05127974930755122</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>Trạm lồng thép cọc + Coupler</t>
+        </is>
+      </c>
+      <c r="P16" s="13" t="inlineStr">
         <is>
           <t>OPTIMAL</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Ø10</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Thép cuộn, đai xoắn cọc khoan nhồi, bản mặt cầu</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>12278</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>19404.38</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>1690</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>12199.9</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>315.68</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>0.0159654073736914</v>
-      </c>
-      <c r="K8" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>Trạm máy duỗi uốn tự động CNC</t>
-        </is>
-      </c>
-      <c r="N8" s="12" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Ø28</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Thép thân đặc mố M1, M2 và xà mũ trụ T1, T2</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>387</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>3507.2</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>352</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>19908.3</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>610.91</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>0.1483379467754468</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>Trạm cắt dập đầu ren mố trụ</t>
+        </is>
+      </c>
+      <c r="P17" s="13" t="inlineStr">
         <is>
           <t>OPTIMAL</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Ø12</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Thép thanh vằn cấu tạo, lưới phân bố</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>76014</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>138236.34</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>11847</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>123085.6</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>52.73</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>0.0003803912996113553</v>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="L9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>Trạm máy cắt đa thanh Shearline</t>
-        </is>
-      </c>
-      <c r="N9" s="12" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Ø32</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Thép chủ lớp đáy bệ móng chịu uốn chính</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>1754</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>19129.99</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>1754</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>129554.1</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>1389.02</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>0.06768499839195392</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>558</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>Trạm cắt uốn thanh siêu trường</t>
+        </is>
+      </c>
+      <c r="P18" s="13" t="inlineStr">
         <is>
           <t>OPTIMAL</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Ø14</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Thép sườn/cánh dầm Super-T, bản mặt cầu</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>1875</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>22250.65</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>201</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>2840.8</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>0.001362843900157333</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>Trạm máy cắt đa thanh Shearline</t>
-        </is>
-      </c>
-      <c r="N10" s="12" t="inlineStr">
-        <is>
-          <t>OPTIMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Ø16</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Thép sườn dầm Super-T, dầm ngang, bản mặt cầu</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>35366</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>149522.14</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>12813</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>236561.3</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>8867.51</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>0.05915136936911697</v>
-      </c>
-      <c r="K11" s="11" t="n">
-        <v>88</v>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>Trạm máy cắt phân đoạn lớn</t>
-        </is>
-      </c>
-      <c r="N11" s="12" t="inlineStr">
-        <is>
-          <t>OPTIMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Ø18</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Thép thân mố, thân trụ, bản mặt cầu</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>6917</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>36145.54</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>1335</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>31207.8</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>531.09</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>0.03400147251832645</v>
-      </c>
-      <c r="K12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="L12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>Trạm cắt uốn định hình bệ/thân</t>
-        </is>
-      </c>
-      <c r="N12" s="12" t="inlineStr">
-        <is>
-          <t>OPTIMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Ø20</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Thép phân bố bệ mố, bệ trụ T1, T2</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>1995</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>7784.14</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>903</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>26053.5</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>2775.51</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>0.2627050382864337</v>
-      </c>
-      <c r="K13" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="L13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>Trạm cắt uốn định hình móng</t>
-        </is>
-      </c>
-      <c r="N13" s="12" t="inlineStr">
-        <is>
-          <t>OPTIMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Ø22</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Thép tăng cường chịu lực xà mũ, dầm ngang</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>425</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>2883.33</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>322</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>11241.9</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>883.55</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>0.2345259330041939</v>
-      </c>
-      <c r="K14" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="L14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>Trạm cắt uốn thanh nặng</t>
-        </is>
-      </c>
-      <c r="N14" s="12" t="inlineStr">
-        <is>
-          <t>OPTIMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Ø25</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Thép chủ cọc khoan nhồi D1200, liên tục nhiệt</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>2420</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>27636.28</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>2318</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>104495.7</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>225.39</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>0.008310583099193971</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>Trạm lồng thép cọc + Coupler</t>
-        </is>
-      </c>
-      <c r="N15" s="12" t="inlineStr">
-        <is>
-          <t>OPTIMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Ø28</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Thép thân đặc mố M1, M2 và xà mũ trụ T1, T2</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>11589.94</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>765</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>43266.7</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>1023.42</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>0.1143427741466957</v>
-      </c>
-      <c r="K16" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>Trạm cắt dập đầu ren mố trụ</t>
-        </is>
-      </c>
-      <c r="N16" s="12" t="inlineStr">
-        <is>
-          <t>OPTIMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Ø32</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Thép chủ lớp đáy bệ móng chịu uốn chính</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>1782</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>17878.25</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>971</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>71720.10000000001</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>469.4</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>0.04131778851655268</v>
-      </c>
-      <c r="K17" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>Trạm cắt uốn thanh siêu trường</t>
-        </is>
-      </c>
-      <c r="N17" s="12" t="inlineStr">
-        <is>
-          <t>OPTIMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Ø15.2 (Cáp DƯL)</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>Cáp DƯL 7 sợi ASTM A416 Gr270 căng kéo dầm Super-T</t>
         </is>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E19" s="16" t="n">
         <v>660</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>25212</v>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>- (Cuộn cuộn)</t>
         </is>
       </c>
-      <c r="H18" s="17" t="n">
+      <c r="H19" s="18" t="n">
         <v>27783.6</v>
       </c>
-      <c r="I18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="13" t="inlineStr">
+      <c r="I19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L18" s="13" t="inlineStr">
+      <c r="L19" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M18" s="14" t="inlineStr">
+      <c r="M19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="15" t="inlineStr">
         <is>
           <t>Trạm căng kéo cáp DƯL chuyên dụng</t>
         </is>
       </c>
-      <c r="N18" s="13" t="inlineStr">
+      <c r="P19" s="14" t="inlineStr">
         <is>
           <t>THEO CUỘN</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="19" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr"/>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr"/>
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>TOÀN BỘ CÔNG TRÌNH CẦU KM19+529.080</t>
         </is>
       </c>
-      <c r="E19" s="21" t="n">
-        <v>142250</v>
-      </c>
-      <c r="F19" s="22" t="n">
-        <v>459086.738</v>
-      </c>
-      <c r="G19" s="21" t="n">
-        <v>33212</v>
-      </c>
-      <c r="H19" s="23" t="n">
-        <v>690674.1899999999</v>
-      </c>
-      <c r="I19" s="22" t="n">
-        <v>15149.952</v>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>0.03898794689593196</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>201</v>
-      </c>
-      <c r="L19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="20" t="inlineStr">
+      <c r="E20" s="22" t="n">
+        <v>143208</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>453959.596</v>
+      </c>
+      <c r="G20" s="22" t="n">
+        <v>37682</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>792221.3999999999</v>
+      </c>
+      <c r="I20" s="23" t="n">
+        <v>11579.329</v>
+      </c>
+      <c r="J20" s="25" t="n">
+        <v>0.02626416430434264</v>
+      </c>
+      <c r="K20" s="26" t="n">
+        <v>280</v>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>5629</v>
+      </c>
+      <c r="M20" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="21" t="inlineStr">
         <is>
           <t>Đồng bộ bãi gia công 5 trạm</t>
         </is>
       </c>
-      <c r="N19" s="19" t="inlineStr">
+      <c r="P20" s="20" t="inlineStr">
         <is>
           <t>HOÀN TẤT</t>
         </is>

--- a/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/00_BANG_TONG_HOP_CAT_THEP_THEO_PHI.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/00_BANG_TONG_HOP_CAT_THEP_THEO_PHI.xlsx
@@ -844,25 +844,25 @@
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>77681</v>
+        <v>21068</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>138949.04</v>
+        <v>34620.27</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>11906</v>
+        <v>2967</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>123698.6</v>
+        <v>30825.9</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>22.28</v>
+        <v>3.13</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0.0001599638765773488</v>
+        <v>9.007919018030242e-05</v>
       </c>
       <c r="K10" s="12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L10" s="12" t="n">
         <v>0</v>
@@ -954,25 +954,25 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>36493</v>
+        <v>15163</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>149520.08</v>
+        <v>64138.66</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>13415</v>
+        <v>5521</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>247675.8</v>
+        <v>101932</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>7317.57</v>
+        <v>406.37</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.04662197246990389</v>
+        <v>0.006290991505626536</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>492</v>
@@ -1009,25 +1009,25 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>7530</v>
+        <v>6270</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>37602.6</v>
+        <v>33343.8</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>3227</v>
+        <v>2873</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>75436.3</v>
+        <v>67161</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>123.61</v>
+        <v>245.14</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>0.00327384594195874</v>
+        <v>0.007292683724984456</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>1636</v>
@@ -1064,22 +1064,22 @@
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>3897</v>
+        <v>3537</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>4703.04</v>
+        <v>4663.44</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>11656.3</v>
+        <v>11598.6</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>6.29</v>
+        <v>24.29</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.001331767792163831</v>
+        <v>0.005163286133435387</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>11</v>
@@ -1284,22 +1284,22 @@
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>1754</v>
+        <v>1214</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>19129.99</v>
+        <v>13465.39</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>1754</v>
+        <v>1214</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>129554.1</v>
+        <v>89668.60000000001</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>1389.02</v>
+        <v>735.62</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>0.06768499839195392</v>
+        <v>0.05179022515101592</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>21</v>
@@ -1398,25 +1398,25 @@
         </is>
       </c>
       <c r="E20" s="22" t="n">
-        <v>143208</v>
+        <v>63105</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>453959.596</v>
+        <v>254286.406</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>37682</v>
+        <v>19953</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>792221.3999999999</v>
+        <v>505386.4299999999</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>11579.329</v>
+        <v>4135.089</v>
       </c>
       <c r="J20" s="25" t="n">
-        <v>0.02626416430434264</v>
+        <v>0.01771294593576957</v>
       </c>
       <c r="K20" s="26" t="n">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="L20" s="26" t="n">
         <v>5629</v>

--- a/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/00_BANG_TONG_HOP_CAT_THEP_THEO_PHI.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/00_BANG_TONG_HOP_CAT_THEP_THEO_PHI.xlsx
@@ -734,25 +734,25 @@
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>81</v>
+        <v>292</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>60.59</v>
+        <v>253.86</v>
       </c>
       <c r="G8" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>0.008492618492618493</v>
+      </c>
+      <c r="K8" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>0.1315242165242165</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="L8" s="12" t="n">
         <v>0</v>
@@ -789,25 +789,25 @@
         </is>
       </c>
       <c r="E9" s="8" t="n">
-        <v>7419</v>
+        <v>7939</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>19352.59</v>
+        <v>19518.99</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>1663</v>
+        <v>1672</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>12005</v>
+        <v>12070</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>68.81</v>
+        <v>5.16</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>0.003536601035097728</v>
+        <v>0.0002636179609863821</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L9" s="12" t="n">
         <v>1384</v>
@@ -844,25 +844,25 @@
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>21068</v>
+        <v>22312</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>34620.27</v>
+        <v>35138.1</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>2967</v>
+        <v>3012</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>30825.9</v>
+        <v>31293.5</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>3.13</v>
+        <v>5.8</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>9.007919018030242e-05</v>
+        <v>0.0001646689594896766</v>
       </c>
       <c r="K10" s="12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L10" s="12" t="n">
         <v>0</v>
@@ -899,25 +899,25 @@
         </is>
       </c>
       <c r="E11" s="8" t="n">
-        <v>3856</v>
+        <v>3925</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>28699.85</v>
+        <v>28740.21</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>34811.1</v>
+        <v>34825.2</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>102.73</v>
+        <v>73.72</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>0.003564758424685343</v>
+        <v>0.002557199744699745</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>1512</v>
@@ -954,25 +954,25 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>15163</v>
+        <v>15282</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>64138.66</v>
+        <v>64291.88</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>5521</v>
+        <v>5529</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>101932</v>
+        <v>102079.7</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>406.37</v>
+        <v>346.19</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.006290991505626536</v>
+        <v>0.005351657847588395</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>492</v>
@@ -1009,28 +1009,28 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>6270</v>
+        <v>6594</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>33343.8</v>
+        <v>35215.98</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>2873</v>
+        <v>3035</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>67161</v>
+        <v>70948</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>245.14</v>
+        <v>267.01</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>0.007292683724984456</v>
+        <v>0.007519311733479773</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>1636</v>
+        <v>1744</v>
       </c>
       <c r="M13" s="8" t="n">
         <v>0</v>
@@ -1174,25 +1174,25 @@
         </is>
       </c>
       <c r="E16" s="8" t="n">
-        <v>2808</v>
+        <v>3190</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>25549.61</v>
+        <v>26915.95</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>2302</v>
+        <v>2419</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>103774.4</v>
+        <v>109048.8</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>1381.14</v>
+        <v>1382.37</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>0.05127974930755122</v>
+        <v>0.04884313289025979</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>24</v>
@@ -1398,28 +1398,28 @@
         </is>
       </c>
       <c r="E20" s="22" t="n">
-        <v>63105</v>
+        <v>65974</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>254286.406</v>
+        <v>258596.013</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>19953</v>
+        <v>20311</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>505386.4299999999</v>
+        <v>515216.1</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>4135.089</v>
+        <v>4000.987</v>
       </c>
       <c r="J20" s="25" t="n">
-        <v>0.01771294593576957</v>
+        <v>0.01683642857834183</v>
       </c>
       <c r="K20" s="26" t="n">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="L20" s="26" t="n">
-        <v>5629</v>
+        <v>5737</v>
       </c>
       <c r="M20" s="22" t="n">
         <v>0</v>

--- a/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/00_BANG_TONG_HOP_CAT_THEP_THEO_PHI.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/00_BANG_TONG_HOP_CAT_THEP_THEO_PHI.xlsx
@@ -954,25 +954,25 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>15282</v>
+        <v>15386</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>64291.88</v>
+        <v>64559.34</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>5529</v>
+        <v>5551</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>102079.7</v>
+        <v>102485.9</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>346.19</v>
+        <v>335.73</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.005351657847588395</v>
+        <v>0.005169300364760642</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>492</v>
@@ -1398,25 +1398,25 @@
         </is>
       </c>
       <c r="E20" s="22" t="n">
-        <v>65974</v>
+        <v>66078</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>258596.013</v>
+        <v>258863.469</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>20311</v>
+        <v>20333</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>515216.1</v>
+        <v>515622.27</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>4000.987</v>
+        <v>3990.521</v>
       </c>
       <c r="J20" s="25" t="n">
-        <v>0.01683642857834183</v>
+        <v>0.01677421782030054</v>
       </c>
       <c r="K20" s="26" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="L20" s="26" t="n">
         <v>5737</v>
